--- a/AAII_Financials/Yearly/CMHHY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CMHHY_YR_FIN.xlsx
@@ -2141,10 +2141,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>191400</v>
+        <v>66600</v>
       </c>
       <c r="E57" s="3">
-        <v>152300</v>
+        <v>47600</v>
       </c>
       <c r="F57" s="3">
         <v>46000</v>
